--- a/data_description_EN.xlsx
+++ b/data_description_EN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weissenberg\Desktop\AOK_Revision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A3B1CF-1992-4671-9AC6-B5036A7EF3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35BC683-938A-4C5F-9305-B6DD5361E378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="3360" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="4035" windowWidth="28785" windowHeight="15360" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="04_AOK_ICD10_GM.txt" sheetId="7" r:id="rId5"/>
     <sheet name="05_AOK_hc_use.txt" sheetId="9" r:id="rId6"/>
     <sheet name="06_AOK_full_ins_pop.txt" sheetId="10" r:id="rId7"/>
-    <sheet name="Analysis_DF_AFTER_PSM" sheetId="11" r:id="rId8"/>
+    <sheet name="Analysis_DF" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -192,16 +192,10 @@
     <t>(printed to log only, not saved as .dta)</t>
   </si>
   <si>
-    <t>- 07_Anal_DS.do merges files 1 to 5 from above into anal_df_yyyyq.dta / anal_df_y.dta (one row per person-quarter / person-year).</t>
-  </si>
-  <si>
     <t>- 08_Study_Size.do applies eligibility criteria and builds psm_case_pool.dta / psm_mc_control_pool.dta.</t>
   </si>
   <si>
     <t>- 09_PSM.do performs 1:2 propensity-score matching (on age, female, german, spatial_str) and aligns event time -&gt; event_case_mc.dta.</t>
-  </si>
-  <si>
-    <t>- 10_Anal.do estimates prevalence and conditional odds ratios -&gt; 02_results/03_tables/prev_pooled.csv and cors_pooled.csv.</t>
   </si>
   <si>
     <r>
@@ -776,9 +770,6 @@
     <t xml:space="preserve">The Analysis Dataframe after PSM in Do-File 9 </t>
   </si>
   <si>
-    <t>Analysis_DF_AFTER_PSM</t>
-  </si>
-  <si>
     <t>Any Mental and behavioural disorders; excluding F63.0 (ICD-10-GM: F00-F99; excluding F63.0)</t>
   </si>
   <si>
@@ -807,6 +798,15 @@
   </si>
   <si>
     <t xml:space="preserve">1 if first GD diag in that year </t>
+  </si>
+  <si>
+    <t>- 10_Analysis.do estimates prevalence and conditional odds ratios -&gt; 02_results/03_tables/prev_pooled.csv and cors_pooled.csv.</t>
+  </si>
+  <si>
+    <t>Analysis_DF</t>
+  </si>
+  <si>
+    <t>- 07_Analysis_DS.do merges files 1 to 5 from above into analysis_df_yyyyq.dta / analysis_df_y.dta (one row per person-quarter / person-year).</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -965,7 +965,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1006,29 +1006,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1040,13 +1017,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1276,7 +1251,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1291,6 +1266,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1309,7 +1285,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1328,7 +1304,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1370,6 +1346,100 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1581,99 +1651,27 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1687,11 +1685,13 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1707,100 +1707,100 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52E47E51-AD89-40E7-98F6-5BBDFEC186D4}" name="Table1" displayName="Table1" ref="A1:F15" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52E47E51-AD89-40E7-98F6-5BBDFEC186D4}" name="Table1" displayName="Table1" ref="A1:F15" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{43ECA6D4-D450-4E7A-82F8-7F5F24AF8B24}" name="Raw file" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{E602866C-60B8-4B17-900F-9E57F53B7D75}" name="Content" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{3D400CB9-FF47-443C-BB68-8672C0655F18}" name="Processed by " dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{F3DFB674-BB1E-4711-B84D-0BEAFC77408C}" name="Output dataset (01_data_work)" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{22591ECB-1DE9-423A-8FBA-597EBB37E40D}" name="Status / Notes" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{CDEB53BC-8137-4612-B8A6-428F06B2D735}" name="Detail sheet" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{43ECA6D4-D450-4E7A-82F8-7F5F24AF8B24}" name="Raw file" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{E602866C-60B8-4B17-900F-9E57F53B7D75}" name="Content" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{3D400CB9-FF47-443C-BB68-8672C0655F18}" name="Processed by " dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{F3DFB674-BB1E-4711-B84D-0BEAFC77408C}" name="Output dataset (01_data_work)" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{22591ECB-1DE9-423A-8FBA-597EBB37E40D}" name="Status / Notes" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{CDEB53BC-8137-4612-B8A6-428F06B2D735}" name="Detail sheet" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5258FEA6-E456-4571-887F-A9A5189A1A5C}" name="Table2" displayName="Table2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5258FEA6-E456-4571-887F-A9A5189A1A5C}" name="Table2" displayName="Table2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E74873D5-DD03-483A-A51B-CFBE1B2D5EEC}" name="variable name original" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{0DCED0CE-0881-49CD-A2DE-14215CD90757}" name="in English" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{C738BD01-5CD8-45A2-8AB1-F1AFFE694641}" name="Explanation" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{B3ED0D4F-8960-4652-A75B-9DA8A4E83A5C}" name="Used?" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{E74873D5-DD03-483A-A51B-CFBE1B2D5EEC}" name="variable name original" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{0DCED0CE-0881-49CD-A2DE-14215CD90757}" name="in English" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{C738BD01-5CD8-45A2-8AB1-F1AFFE694641}" name="Explanation" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{B3ED0D4F-8960-4652-A75B-9DA8A4E83A5C}" name="Used?" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9545EF26-C39E-47BB-9358-0A10D1C21484}" name="Table24" displayName="Table24" ref="A1:D11" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9545EF26-C39E-47BB-9358-0A10D1C21484}" name="Table24" displayName="Table24" ref="A1:D11" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D62E91F5-1606-4AE6-A122-246F5A18A4F5}" name="variable name original" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{7F14E80E-0557-4D15-87DB-54205B8FF0DE}" name="in English" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{DDE08AE6-6E8E-47FD-A585-B84BCBBCC542}" name="Explanation" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{27EC74D1-77F3-4F87-B841-1858CF5979CB}" name="Used?" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{D62E91F5-1606-4AE6-A122-246F5A18A4F5}" name="variable name original" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{7F14E80E-0557-4D15-87DB-54205B8FF0DE}" name="in English" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{DDE08AE6-6E8E-47FD-A585-B84BCBBCC542}" name="Explanation" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{27EC74D1-77F3-4F87-B841-1858CF5979CB}" name="Used?" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4524532D-9373-4B3C-A95C-33652CBD427D}" name="Table245" displayName="Table245" ref="A1:D9" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4524532D-9373-4B3C-A95C-33652CBD427D}" name="Table245" displayName="Table245" ref="A1:D9" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4856A11C-4209-4A9B-B9F9-780B74A13B22}" name="variable name original" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{67A43F02-4AF8-4F54-B0EB-01C15FBE3C3F}" name="in English" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{93A318EE-5942-4DB1-A3B4-BD726B018509}" name="Explanation" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{5B891C19-0AA9-4DC4-8DEE-20DDE000AC4E}" name="Used?" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{4856A11C-4209-4A9B-B9F9-780B74A13B22}" name="variable name original" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{67A43F02-4AF8-4F54-B0EB-01C15FBE3C3F}" name="in English" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{93A318EE-5942-4DB1-A3B4-BD726B018509}" name="Explanation" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{5B891C19-0AA9-4DC4-8DEE-20DDE000AC4E}" name="Used?" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1EFC8E1D-5276-4D16-A75B-69C3A077D372}" name="Table2456" displayName="Table2456" ref="A1:D5" totalsRowShown="0" headerRowDxfId="24" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1EFC8E1D-5276-4D16-A75B-69C3A077D372}" name="Table2456" displayName="Table2456" ref="A1:D5" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8E191696-6339-48D4-8FC9-9FCA83236EF1}" name="variable name original" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{15CD3948-4AB3-4C86-B633-9BB1F1ED8366}" name="in English" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{E8E7C3DB-9EC7-4672-AB94-09EC3ECE7DC4}" name="Explanation" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{B5786516-E5DF-4604-ABE3-4C1CC6CE340C}" name="Used?" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8E191696-6339-48D4-8FC9-9FCA83236EF1}" name="variable name original" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{15CD3948-4AB3-4C86-B633-9BB1F1ED8366}" name="in English" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{E8E7C3DB-9EC7-4672-AB94-09EC3ECE7DC4}" name="Explanation" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{B5786516-E5DF-4604-ABE3-4C1CC6CE340C}" name="Used?" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9B7041AD-923B-4A9B-B026-E733C96230F1}" name="Table24567" displayName="Table24567" ref="A1:D10" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9B7041AD-923B-4A9B-B026-E733C96230F1}" name="Table24567" displayName="Table24567" ref="A1:D10" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{37C357A6-383F-415B-A383-FA5D660458AA}" name="variable name original" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{57EDF819-651B-41A2-B046-CDFEBD8980AB}" name="in English" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{0FFFC227-C76C-4B18-901A-F23AC532C1DC}" name="Explanation" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{76BE2A9A-0206-40CE-97CF-AB99B857A53D}" name="Used?" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{37C357A6-383F-415B-A383-FA5D660458AA}" name="variable name original" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{57EDF819-651B-41A2-B046-CDFEBD8980AB}" name="in English" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{0FFFC227-C76C-4B18-901A-F23AC532C1DC}" name="Explanation" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{76BE2A9A-0206-40CE-97CF-AB99B857A53D}" name="Used?" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7FFC82AF-2CC1-40EE-BFED-F14C28DE52A6}" name="Table245678" displayName="Table245678" ref="A1:D6" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7FFC82AF-2CC1-40EE-BFED-F14C28DE52A6}" name="Table245678" displayName="Table245678" ref="A1:D6" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{18E1B509-7174-4C55-B0B4-77C52AD22F61}" name="variable name original" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{640BF8DB-5C0B-4249-9536-FB3144603937}" name="in English" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{29EA9B0E-950C-4169-A8BF-002835B9765A}" name="Explanation" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{76CBA1E2-B9FB-4193-A454-0E32B503BF06}" name="Used?" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{18E1B509-7174-4C55-B0B4-77C52AD22F61}" name="variable name original" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{640BF8DB-5C0B-4249-9536-FB3144603937}" name="in English" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{29EA9B0E-950C-4169-A8BF-002835B9765A}" name="Explanation" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{76CBA1E2-B9FB-4193-A454-0E32B503BF06}" name="Used?" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BD6746E1-45AD-482D-808A-EA429878A043}" name="Table12" displayName="Table12" ref="A1:E43" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BD6746E1-45AD-482D-808A-EA429878A043}" name="Table12" displayName="Table12" ref="A1:E43" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A1:E43" xr:uid="{BD6746E1-45AD-482D-808A-EA429878A043}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E5C127E7-EB50-4DA7-B4F9-E3F38D537526}" name="var_name" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{9962293A-0FBC-4A1F-88DE-6F4FF9E01794}" name="var_label" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{BB0E9395-1A07-40BA-8022-DB7F70A5A079}" name="var_min" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{11073FD1-8EC3-434D-9E1E-B8EC9D7D7D51}" name="var_max" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{B6CC84F4-101A-4C83-BED3-D8084A508901}" name="n_missing" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{E5C127E7-EB50-4DA7-B4F9-E3F38D537526}" name="var_name" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{9962293A-0FBC-4A1F-88DE-6F4FF9E01794}" name="var_label" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{BB0E9395-1A07-40BA-8022-DB7F70A5A079}" name="var_min" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{11073FD1-8EC3-434D-9E1E-B8EC9D7D7D51}" name="var_max" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{B6CC84F4-101A-4C83-BED3-D8084A508901}" name="n_missing" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2083,13 +2083,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>19</v>
@@ -2135,7 +2135,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>27</v>
@@ -2215,7 +2215,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>45</v>
@@ -2224,17 +2224,17 @@
     <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2257,7 +2257,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>52</v>
+        <v>245</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -2327,24 +2327,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>
@@ -2352,13 +2352,13 @@
     </row>
     <row r="3" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
@@ -2366,13 +2366,13 @@
     </row>
     <row r="4" spans="1:4" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>12</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>12</v>
@@ -2394,13 +2394,13 @@
     </row>
     <row r="6" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>12</v>
@@ -2408,13 +2408,13 @@
     </row>
     <row r="7" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>12</v>
@@ -2442,24 +2442,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
@@ -2481,13 +2481,13 @@
     </row>
     <row r="4" spans="1:4" ht="156.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>12</v>
@@ -2495,100 +2495,100 @@
     </row>
     <row r="5" spans="1:4" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="D11" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2615,24 +2615,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>
@@ -2643,10 +2643,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
@@ -2654,27 +2654,27 @@
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>12</v>
@@ -2682,55 +2682,55 @@
     </row>
     <row r="6" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="88.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>12</v>
@@ -2760,24 +2760,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>
@@ -2788,10 +2788,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
@@ -2799,13 +2799,13 @@
     </row>
     <row r="4" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>12</v>
@@ -2813,13 +2813,13 @@
     </row>
     <row r="5" spans="1:4" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>12</v>
@@ -2849,24 +2849,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>
@@ -2877,10 +2877,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
@@ -2888,13 +2888,13 @@
     </row>
     <row r="4" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>12</v>
@@ -2902,86 +2902,86 @@
     </row>
     <row r="5" spans="1:4" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3008,13 +3008,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3113,24 +3113,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C2" s="8">
         <v>3</v>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C3" s="8">
         <v>2011</v>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C4" s="8">
         <v>0</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C5" s="8">
         <v>1924</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C6" s="8">
         <v>13</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -3229,10 +3229,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C8" s="8">
         <v>0</v>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -3263,10 +3263,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C10" s="8">
         <v>0</v>
@@ -3280,10 +3280,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C11" s="8">
         <v>2014</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C12" s="8">
         <v>0</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -3331,10 +3331,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C14" s="8">
         <v>0</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C16" s="8">
         <v>0</v>
@@ -3382,10 +3382,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C18" s="8">
         <v>0</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C20" s="8">
         <v>0</v>
@@ -3450,10 +3450,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C22" s="8">
         <v>0</v>
@@ -3484,10 +3484,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" s="8">
         <v>0</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C24" s="8">
         <v>0</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C25" s="8">
         <v>0</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C26" s="8">
         <v>0</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C27" s="8">
         <v>0</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C28" s="8">
         <v>0</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C29" s="8">
         <v>0</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C31" s="8">
         <v>1</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C32" s="8">
         <v>1</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C33" s="8">
         <v>0</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C34" s="8">
         <v>2014</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C35" s="8">
         <v>0</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C36" s="8">
         <v>0</v>
@@ -3722,10 +3722,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C37" s="8">
         <v>18</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C38" s="8">
         <v>47</v>
@@ -3756,10 +3756,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C39" s="8">
         <v>-5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C40" s="8">
         <v>0</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C41" s="8">
         <v>2014</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C42" s="8">
         <v>1</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C43" s="8">
         <v>0</v>

--- a/data_description_EN.xlsx
+++ b/data_description_EN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weissenberg\Desktop\AOK_Revision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35BC683-938A-4C5F-9305-B6DD5361E378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F939FD49-36FC-436A-8F21-1B02EDEE0053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="4035" windowWidth="28785" windowHeight="15360" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="4035" windowWidth="28785" windowHeight="15360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="2" r:id="rId1"/>
@@ -791,9 +791,6 @@
     <t xml:space="preserve">Used for Analysis </t>
   </si>
   <si>
-    <t>0 = age/sex-matched control group, 1 = GD (gambling disorder) analysis group, 2 = unmatched random-sample control (added during the revision; dropped again in 08_Study_Size.do)</t>
-  </si>
-  <si>
     <t xml:space="preserve">NO, bc missing not at random </t>
   </si>
   <si>
@@ -807,6 +804,9 @@
   </si>
   <si>
     <t>- 07_Analysis_DS.do merges files 1 to 5 from above into analysis_df_yyyyq.dta / analysis_df_y.dta (one row per person-quarter / person-year).</t>
+  </si>
+  <si>
+    <t>0 = age/sex-matched control group, 1 = GD (gambling disorder) analysis group, 2 = unmatched random-sample control (added during the revision; dropped again in 07_Study_Size.do)</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2234,7 @@
         <v>241</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,7 +2257,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2358,7 +2358,7 @@
         <v>61</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
@@ -2691,7 +2691,7 @@
         <v>108</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2705,7 +2705,7 @@
         <v>111</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -3691,7 +3691,7 @@
         <v>215</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C35" s="8">
         <v>0</v>
